--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_UiHotKot/lang_UiHotKot__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_UiHotKot/lang_UiHotKot__ui__part_0001.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Inspect</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Xử lý vật phẩm</t>
+          <t>Thao tác vật phẩm</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Increase</t>
+          <t>Tăng</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Decrease</t>
+          <t>Giảm</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Hạng Hợp Xướng</t>
+          <t>Hạng Hợp Ca</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Sao Chép ID</t>
+          <t>Sao chép ID</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Kiểm tra vật phẩm</t>
+          <t>Xem vật phẩm</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Tối đa</t>
+          <t>Max</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Hoàn tất</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Character Tiếp Theo</t>
+          <t>Nhân vật tiếp theo</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Đọc</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Chọn nhân vật</t>
+          <t>Chọn Nhân Vật</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Shortlist</t>
+          <t>Danh Sách Rút Gọn</t>
         </is>
       </c>
     </row>
